--- a/config/_TableConfig/!beans__.xlsx
+++ b/config/_TableConfig/!beans__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26490" windowHeight="13000"/>
+    <workbookView windowHeight="15120"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="127">
   <si>
     <t>##var</t>
   </si>
@@ -362,7 +362,7 @@
     <t>奇物信息</t>
   </si>
   <si>
-    <t>Combat.SquadStance</t>
+    <t>Combat.SquadFormation</t>
   </si>
   <si>
     <t>战队队形</t>
@@ -384,6 +384,30 @@
   </si>
   <si>
     <t>列</t>
+  </si>
+  <si>
+    <t>Character.Asset</t>
+  </si>
+  <si>
+    <t>prefab</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>预制体</t>
+  </si>
+  <si>
+    <t>squadPrefab</t>
+  </si>
+  <si>
+    <t>小队预制体</t>
+  </si>
+  <si>
+    <t>icon</t>
+  </si>
+  <si>
+    <t>图标</t>
   </si>
 </sst>
 </file>
@@ -400,7 +424,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -418,20 +442,27 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="等线"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -439,14 +470,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -454,7 +485,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -462,7 +493,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -470,7 +501,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -478,7 +509,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -486,22 +517,15 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -509,7 +533,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -517,14 +541,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -532,42 +556,42 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -581,6 +605,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -588,12 +618,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -890,37 +914,37 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
@@ -938,7 +962,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1020,80 +1044,74 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="23" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="22" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="16" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="22" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1362,8 +1380,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P41"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <dimension ref="A1:P51"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="28.8181818181818" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
@@ -1374,1238 +1392,1409 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2" t="s">
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2" t="s">
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="O3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P3" s="2"/>
+      <c r="P3" s="3"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="2"/>
-      <c r="B4" s="3" t="s">
+      <c r="A4" s="3"/>
+      <c r="B4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3" t="s">
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="3" t="str">
-        <f t="shared" ref="G4:G8" si="0">F4</f>
+      <c r="G4" s="1" t="str">
+        <f>F4</f>
         <v>骰子</v>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3" t="s">
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3" t="s">
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="O4" s="3" t="str">
-        <f t="shared" ref="O4:O23" si="1">N4</f>
+      <c r="O4" s="1" t="str">
+        <f>N4</f>
         <v>数量</v>
       </c>
-      <c r="P4" s="3"/>
+      <c r="P4" s="1"/>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="4"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5" t="s">
+      <c r="A5" s="5"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="K5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5" t="s">
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O5" s="5" t="str">
-        <f t="shared" si="1"/>
+      <c r="O5" s="1" t="str">
+        <f>N5</f>
         <v>骰子面数</v>
       </c>
-      <c r="P5" s="5"/>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="A6" s="4"/>
-      <c r="B6" s="6" t="s">
-        <v>30</v>
-      </c>
+      <c r="P5" s="1"/>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:16">
+      <c r="B6" s="6"/>
       <c r="C6" s="6"/>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
-      <c r="F6" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>伤害</v>
-      </c>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
-      <c r="J6" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>22</v>
-      </c>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
-      <c r="N6" s="6" t="s">
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" s="5"/>
+      <c r="B7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="1" t="str">
+        <f>F7</f>
+        <v>伤害</v>
+      </c>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="O6" s="6" t="str">
+      <c r="O7" s="1" t="str">
+        <f>N7</f>
+        <v>数值</v>
+      </c>
+      <c r="P7" s="1"/>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" s="5"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O8" s="1" t="str">
+        <f>N8</f>
+        <v>类型</v>
+      </c>
+      <c r="P8" s="1"/>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:16">
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="6"/>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" s="5"/>
+      <c r="B10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="1" t="str">
+        <f>F10</f>
+        <v>角色预设</v>
+      </c>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O10" s="1" t="str">
+        <f t="shared" ref="O10:O15" si="0">N10</f>
+        <v>能力值</v>
+      </c>
+      <c r="P10" s="1"/>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11" s="5"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="O11" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>伤害抗性</v>
+      </c>
+      <c r="P11" s="1"/>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" s="5"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O12" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>护甲等级</v>
+      </c>
+      <c r="P12" s="1"/>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13" s="5"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O13" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>移动力</v>
+      </c>
+      <c r="P13" s="1"/>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14" s="5"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="O14" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>先攻</v>
+      </c>
+      <c r="P14" s="1"/>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" s="5"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O15" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>能力</v>
+      </c>
+      <c r="P15" s="1"/>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16" s="5"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="6"/>
+      <c r="P16" s="6"/>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17" s="5"/>
+      <c r="B17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G17" s="1" t="str">
+        <f>F17</f>
+        <v>能力值</v>
+      </c>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O17" s="1" t="str">
+        <f>N17</f>
+        <v>力量</v>
+      </c>
+      <c r="P17" s="1"/>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18" s="5"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="O18" s="1" t="str">
+        <f>N18</f>
+        <v>敏捷</v>
+      </c>
+      <c r="P18" s="1"/>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19" s="5"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O19" s="1" t="str">
+        <f>N19</f>
+        <v>体质</v>
+      </c>
+      <c r="P19" s="1"/>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20" s="5"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="O20" s="1" t="str">
+        <f>N20</f>
+        <v>智力</v>
+      </c>
+      <c r="P20" s="1"/>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21" s="5"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="O21" s="1" t="str">
+        <f>N21</f>
+        <v>感知</v>
+      </c>
+      <c r="P21" s="1"/>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22" s="5"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="6"/>
+      <c r="P22" s="6"/>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23" s="5"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="O23" s="1" t="str">
+        <f>N23</f>
+        <v>魅力</v>
+      </c>
+      <c r="P23" s="1"/>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24" s="5"/>
+      <c r="B24" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G24" s="1" t="str">
+        <f t="shared" ref="G24:G29" si="1">F24</f>
+        <v>预设角色道具</v>
+      </c>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="O24" s="1" t="str">
+        <f>N24</f>
+        <v>主手</v>
+      </c>
+      <c r="P24" s="1"/>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25" s="5"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="O25" s="1" t="str">
+        <f>N25</f>
+        <v>副手</v>
+      </c>
+      <c r="P25" s="1"/>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26" s="5"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O26" s="1" t="str">
+        <f>N26</f>
+        <v>甲</v>
+      </c>
+      <c r="P26" s="1"/>
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27" s="5"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="O27" s="1" t="str">
+        <f>N27</f>
+        <v>奇物</v>
+      </c>
+      <c r="P27" s="1"/>
+    </row>
+    <row r="28" spans="1:16">
+      <c r="A28" s="7"/>
+      <c r="B28" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G28" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>数值</v>
-      </c>
-      <c r="P6" s="6"/>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="A7" s="4"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O7" s="6" t="str">
+        <v>最大生命值</v>
+      </c>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="A29" s="5"/>
+      <c r="B29" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G29" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>类型</v>
-      </c>
-      <c r="P7" s="6"/>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="A8" s="4"/>
-      <c r="B8" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="G8" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>角色预设</v>
-      </c>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="O8" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>能力值</v>
-      </c>
-      <c r="P8" s="5"/>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="A9" s="4"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="O9" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>伤害抗性</v>
-      </c>
-      <c r="P9" s="5"/>
-    </row>
-    <row r="10" spans="1:16">
-      <c r="A10" s="4"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5" t="s">
+        <v>骰子生命值</v>
+      </c>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O29" s="1" t="str">
+        <f>N29</f>
+        <v>骰子</v>
+      </c>
+      <c r="P29" s="1"/>
+    </row>
+    <row r="30" spans="1:16">
+      <c r="A30" s="5"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="O30" s="1" t="str">
+        <f>N30</f>
+        <v>基础值</v>
+      </c>
+      <c r="P30" s="1"/>
+    </row>
+    <row r="31" spans="1:16">
+      <c r="A31" s="5"/>
+      <c r="B31" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G31" s="1" t="str">
+        <f>F31</f>
+        <v>职业生命值</v>
+      </c>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32" s="5"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="6"/>
+      <c r="M32" s="6"/>
+      <c r="N32" s="6"/>
+      <c r="O32" s="6"/>
+      <c r="P32" s="6"/>
+    </row>
+    <row r="33" spans="1:16">
+      <c r="A33" s="5"/>
+      <c r="B33" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G33" s="1" t="str">
+        <f>F33</f>
+        <v>道具信息</v>
+      </c>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
+    </row>
+    <row r="34" spans="1:16">
+      <c r="A34" s="5"/>
+      <c r="B34" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="O34" s="1"/>
+      <c r="P34" s="1"/>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="A35" s="5"/>
+      <c r="B35" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G35" s="1" t="str">
+        <f>F35</f>
+        <v>武器信息</v>
+      </c>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="O35" s="1" t="str">
+        <f>N35</f>
+        <v>基础类型</v>
+      </c>
+      <c r="P35" s="1"/>
+    </row>
+    <row r="36" spans="1:16">
+      <c r="A36" s="5"/>
+      <c r="B36" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G36" s="1" t="str">
+        <f>F36</f>
+        <v>无甲信息</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+      <c r="O36" s="1"/>
+      <c r="P36" s="1"/>
+    </row>
+    <row r="37" spans="1:16">
+      <c r="A37" s="5"/>
+      <c r="B37" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G37" s="1" t="str">
+        <f>F37</f>
+        <v>轻甲信息</v>
+      </c>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="K37" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5" t="s">
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O10" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>护甲等级</v>
-      </c>
-      <c r="P10" s="5"/>
-    </row>
-    <row r="11" spans="1:16">
-      <c r="A11" s="4"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="K11" s="5" t="s">
+      <c r="O37" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P37" s="1"/>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="A38" s="5"/>
+      <c r="B38" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K38" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="O11" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>移动力</v>
-      </c>
-      <c r="P11" s="5"/>
-    </row>
-    <row r="12" spans="1:16">
-      <c r="A12" s="4"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="K12" s="5" t="s">
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P38" s="1"/>
+    </row>
+    <row r="39" spans="1:16">
+      <c r="A39" s="5"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="K39" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="O12" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>先攻</v>
-      </c>
-      <c r="P12" s="5"/>
-    </row>
-    <row r="13" spans="1:16">
-      <c r="A13" s="4"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="K13" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="O13" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>能力</v>
-      </c>
-      <c r="P13" s="5"/>
-    </row>
-    <row r="14" spans="1:16">
-      <c r="A14" s="4"/>
-      <c r="B14" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G14" s="7" t="str">
-        <f>F14</f>
-        <v>能力值</v>
-      </c>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="K14" s="7" t="s">
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="O39" s="1" t="str">
+        <f>N39</f>
+        <v>调整值上限</v>
+      </c>
+      <c r="P39" s="1"/>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="A40" s="5"/>
+      <c r="B40" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G40" s="1" t="str">
+        <f>F40</f>
+        <v>重甲信息</v>
+      </c>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K40" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="O14" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>力量</v>
-      </c>
-      <c r="P14" s="7"/>
-    </row>
-    <row r="15" spans="1:16">
-      <c r="A15" s="4"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="K15" s="7" t="s">
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O40" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P40" s="1"/>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="A41" s="5"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="K41" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="O15" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>敏捷</v>
-      </c>
-      <c r="P15" s="7"/>
-    </row>
-    <row r="16" spans="1:16">
-      <c r="A16" s="4"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="K16" s="7" t="s">
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="O41" s="1" t="str">
+        <f>N41</f>
+        <v>装备力量需求</v>
+      </c>
+      <c r="P41" s="1"/>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="A42" s="5"/>
+      <c r="B42" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="G42" s="1" t="str">
+        <f>F42</f>
+        <v>盾牌信息</v>
+      </c>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K42" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="O16" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>体质</v>
-      </c>
-      <c r="P16" s="7"/>
-    </row>
-    <row r="17" spans="1:16">
-      <c r="A17" s="4"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="K17" s="7" t="s">
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O42" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P42" s="1"/>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43" s="5"/>
+      <c r="B43" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
+      <c r="N43" s="1"/>
+      <c r="O43" s="1"/>
+      <c r="P43" s="1"/>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="A44" s="5"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6"/>
+      <c r="J44" s="6"/>
+      <c r="K44" s="6"/>
+      <c r="L44" s="6"/>
+      <c r="M44" s="6"/>
+      <c r="N44" s="6"/>
+      <c r="O44" s="6"/>
+      <c r="P44" s="6"/>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45" s="5"/>
+      <c r="B45" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="K45" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="O17" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>智力</v>
-      </c>
-      <c r="P17" s="7"/>
-    </row>
-    <row r="18" spans="1:16">
-      <c r="A18" s="4"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="K18" s="7" t="s">
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="O45" s="1" t="str">
+        <f>N45</f>
+        <v>角色id</v>
+      </c>
+      <c r="P45" s="1"/>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46" s="5"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="K46" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="O18" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>感知</v>
-      </c>
-      <c r="P18" s="7"/>
-    </row>
-    <row r="19" spans="1:16">
-      <c r="A19" s="4"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="K19" s="7" t="s">
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
+      <c r="N46" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="O46" s="1" t="str">
+        <f>N46</f>
+        <v>排</v>
+      </c>
+      <c r="P46" s="1"/>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47" s="5"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="K47" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L19" s="7"/>
-      <c r="M19" s="7"/>
-      <c r="N19" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="O19" s="7" t="str">
-        <f t="shared" si="1"/>
-        <v>魅力</v>
-      </c>
-      <c r="P19" s="7"/>
-    </row>
-    <row r="20" spans="1:16">
-      <c r="A20" s="4"/>
-      <c r="B20" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="G20" s="5" t="str">
-        <f t="shared" ref="G20:G25" si="2">F20</f>
-        <v>预设角色道具</v>
-      </c>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="K20" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="L20" s="5"/>
-      <c r="M20" s="5"/>
-      <c r="N20" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="O20" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>主手</v>
-      </c>
-      <c r="P20" s="5"/>
-    </row>
-    <row r="21" spans="1:16">
-      <c r="A21" s="4"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K21" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="L21" s="5"/>
-      <c r="M21" s="5"/>
-      <c r="N21" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="O21" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>副手</v>
-      </c>
-      <c r="P21" s="5"/>
-    </row>
-    <row r="22" spans="1:16">
-      <c r="A22" s="4"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="K22" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="L22" s="5"/>
-      <c r="M22" s="5"/>
-      <c r="N22" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="O22" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>甲</v>
-      </c>
-      <c r="P22" s="5"/>
-    </row>
-    <row r="23" spans="1:16">
-      <c r="A23" s="4"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="K23" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="L23" s="5"/>
-      <c r="M23" s="5"/>
-      <c r="N23" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="O23" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>奇物</v>
-      </c>
-      <c r="P23" s="5"/>
-    </row>
-    <row r="24" spans="1:16">
-      <c r="A24" s="8"/>
-      <c r="B24" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="G24" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>最大生命值</v>
-      </c>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="7"/>
-      <c r="O24" s="7"/>
-      <c r="P24" s="7"/>
-    </row>
-    <row r="25" spans="1:16">
-      <c r="A25" s="4"/>
-      <c r="B25" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="G25" s="7" t="str">
-        <f t="shared" si="2"/>
-        <v>骰子生命值</v>
-      </c>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="K25" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="L25" s="7"/>
-      <c r="M25" s="7"/>
-      <c r="N25" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="O25" s="7" t="str">
-        <f t="shared" ref="O25:O30" si="3">N25</f>
-        <v>骰子</v>
-      </c>
-      <c r="P25" s="7"/>
-    </row>
-    <row r="26" spans="1:16">
-      <c r="A26" s="4"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="K26" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7"/>
-      <c r="N26" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="O26" s="7" t="str">
-        <f t="shared" si="3"/>
-        <v>基础值</v>
-      </c>
-      <c r="P26" s="7"/>
-    </row>
-    <row r="27" spans="1:16">
-      <c r="A27" s="4"/>
-      <c r="B27" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="G27" s="7" t="str">
-        <f t="shared" ref="G27:G32" si="4">F27</f>
-        <v>职业生命值</v>
-      </c>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="7"/>
-      <c r="M27" s="7"/>
-      <c r="N27" s="7"/>
-      <c r="O27" s="7"/>
-      <c r="P27" s="7"/>
-    </row>
-    <row r="28" spans="1:16">
-      <c r="A28" s="4"/>
-      <c r="B28" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="G28" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>道具信息</v>
-      </c>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="5"/>
-      <c r="K28" s="5"/>
-      <c r="L28" s="5"/>
-      <c r="M28" s="5"/>
-      <c r="N28" s="5"/>
-      <c r="O28" s="5"/>
-      <c r="P28" s="5"/>
-    </row>
-    <row r="29" spans="1:16">
-      <c r="A29" s="4"/>
-      <c r="B29" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="H29" s="5"/>
-      <c r="I29" s="5"/>
-      <c r="J29" s="5"/>
-      <c r="K29" s="5"/>
-      <c r="L29" s="5"/>
-      <c r="M29" s="5"/>
-      <c r="N29" s="5"/>
-      <c r="O29" s="5"/>
-      <c r="P29" s="5"/>
-    </row>
-    <row r="30" spans="1:16">
-      <c r="A30" s="4"/>
-      <c r="B30" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="G30" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>武器信息</v>
-      </c>
-      <c r="H30" s="5"/>
-      <c r="I30" s="5"/>
-      <c r="J30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="K30" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="L30" s="5"/>
-      <c r="M30" s="5"/>
-      <c r="N30" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="O30" s="5" t="str">
-        <f t="shared" si="3"/>
-        <v>基础类型</v>
-      </c>
-      <c r="P30" s="5"/>
-    </row>
-    <row r="31" spans="1:16">
-      <c r="A31" s="4"/>
-      <c r="B31" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="G31" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>无甲信息</v>
-      </c>
-      <c r="H31" s="5"/>
-      <c r="I31" s="5"/>
-      <c r="J31" s="5"/>
-      <c r="K31" s="5"/>
-      <c r="L31" s="5"/>
-      <c r="M31" s="5"/>
-      <c r="N31" s="5"/>
-      <c r="O31" s="5"/>
-      <c r="P31" s="5"/>
-    </row>
-    <row r="32" spans="1:16">
-      <c r="A32" s="4"/>
-      <c r="B32" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="G32" s="5" t="str">
-        <f t="shared" si="4"/>
-        <v>轻甲信息</v>
-      </c>
-      <c r="H32" s="5"/>
-      <c r="I32" s="5"/>
-      <c r="J32" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="K32" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L32" s="5"/>
-      <c r="M32" s="5"/>
-      <c r="N32" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="O32" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="P32" s="5"/>
-    </row>
-    <row r="33" spans="1:16">
-      <c r="A33" s="4"/>
-      <c r="B33" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="G33" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="H33" s="5"/>
-      <c r="I33" s="5"/>
-      <c r="J33" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="K33" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L33" s="5"/>
-      <c r="M33" s="5"/>
-      <c r="N33" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="O33" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="P33" s="5"/>
-    </row>
-    <row r="34" spans="1:16">
-      <c r="A34" s="4"/>
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
-      <c r="H34" s="5"/>
-      <c r="I34" s="5"/>
-      <c r="J34" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="K34" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L34" s="5"/>
-      <c r="M34" s="5"/>
-      <c r="N34" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="O34" s="5" t="str">
-        <f t="shared" ref="O34:O41" si="5">N34</f>
-        <v>调整值上限</v>
-      </c>
-      <c r="P34" s="5"/>
-    </row>
-    <row r="35" spans="1:16">
-      <c r="A35" s="4"/>
-      <c r="B35" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="G35" s="5" t="str">
-        <f>F35</f>
-        <v>重甲信息</v>
-      </c>
-      <c r="H35" s="5"/>
-      <c r="I35" s="5"/>
-      <c r="J35" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="K35" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L35" s="5"/>
-      <c r="M35" s="5"/>
-      <c r="N35" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="O35" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="P35" s="5"/>
-    </row>
-    <row r="36" spans="1:16">
-      <c r="A36" s="4"/>
-      <c r="B36" s="5"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5"/>
-      <c r="I36" s="5"/>
-      <c r="J36" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="K36" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L36" s="5"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="O36" s="5" t="str">
-        <f t="shared" si="5"/>
-        <v>装备力量需求</v>
-      </c>
-      <c r="P36" s="5"/>
-    </row>
-    <row r="37" spans="1:16">
-      <c r="A37" s="4"/>
-      <c r="B37" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="G37" s="5" t="str">
-        <f>F37</f>
-        <v>盾牌信息</v>
-      </c>
-      <c r="H37" s="5"/>
-      <c r="I37" s="5"/>
-      <c r="J37" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="K37" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L37" s="5"/>
-      <c r="M37" s="5"/>
-      <c r="N37" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="O37" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="P37" s="5"/>
-    </row>
-    <row r="38" spans="1:16">
-      <c r="A38" s="4"/>
-      <c r="B38" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="H38" s="5"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="5"/>
-      <c r="K38" s="5"/>
-      <c r="L38" s="5"/>
-      <c r="M38" s="5"/>
-      <c r="N38" s="5"/>
-      <c r="O38" s="5"/>
-      <c r="P38" s="5"/>
-    </row>
-    <row r="39" spans="1:16">
-      <c r="A39" s="4"/>
-      <c r="B39" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="G39" s="7"/>
-      <c r="H39" s="7"/>
-      <c r="I39" s="7"/>
-      <c r="J39" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="K39" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="L39" s="7"/>
-      <c r="M39" s="7"/>
-      <c r="N39" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="O39" s="7" t="str">
-        <f t="shared" si="5"/>
-        <v>角色id</v>
-      </c>
-      <c r="P39" s="7"/>
-    </row>
-    <row r="40" spans="1:16">
-      <c r="A40" s="4"/>
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
-      <c r="H40" s="7"/>
-      <c r="I40" s="7"/>
-      <c r="J40" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="K40" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="L40" s="7"/>
-      <c r="M40" s="7"/>
-      <c r="N40" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="O40" s="7" t="str">
-        <f t="shared" si="5"/>
-        <v>排</v>
-      </c>
-      <c r="P40" s="7"/>
-    </row>
-    <row r="41" spans="1:16">
-      <c r="A41" s="4"/>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="7"/>
-      <c r="H41" s="7"/>
-      <c r="I41" s="7"/>
-      <c r="J41" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="K41" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="L41" s="7"/>
-      <c r="M41" s="7"/>
-      <c r="N41" s="7" t="s">
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+      <c r="N47" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="O41" s="7" t="str">
-        <f t="shared" si="5"/>
+      <c r="O47" s="1" t="str">
+        <f>N47</f>
         <v>列</v>
       </c>
-      <c r="P41" s="7"/>
+      <c r="P47" s="1"/>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="6"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="6"/>
+      <c r="J48" s="6"/>
+      <c r="K48" s="6"/>
+      <c r="L48" s="6"/>
+      <c r="M48" s="6"/>
+      <c r="N48" s="6"/>
+      <c r="O48" s="6"/>
+      <c r="P48" s="6"/>
+    </row>
+    <row r="49" spans="2:15">
+      <c r="B49" t="s">
+        <v>119</v>
+      </c>
+      <c r="J49" t="s">
+        <v>120</v>
+      </c>
+      <c r="K49" t="s">
+        <v>121</v>
+      </c>
+      <c r="N49" t="s">
+        <v>122</v>
+      </c>
+      <c r="O49" t="str">
+        <f>N49</f>
+        <v>预制体</v>
+      </c>
+    </row>
+    <row r="50" spans="2:15">
+      <c r="J50" t="s">
+        <v>123</v>
+      </c>
+      <c r="K50" t="s">
+        <v>121</v>
+      </c>
+      <c r="N50" t="s">
+        <v>124</v>
+      </c>
+      <c r="O50" t="str">
+        <f>N50</f>
+        <v>小队预制体</v>
+      </c>
+    </row>
+    <row r="51" spans="2:15">
+      <c r="J51" t="s">
+        <v>125</v>
+      </c>
+      <c r="K51" t="s">
+        <v>121</v>
+      </c>
+      <c r="N51" t="s">
+        <v>126</v>
+      </c>
+      <c r="O51" t="str">
+        <f>N51</f>
+        <v>图标</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
